--- a/planilhas/REDEMAT-dados-do-site.xlsx
+++ b/planilhas/REDEMAT-dados-do-site.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="277">
   <si>
     <t xml:space="preserve">REDEMAT — planilha de manutenção do portal</t>
   </si>
@@ -331,7 +331,7 @@
     <t xml:space="preserve">Núcleo comum</t>
   </si>
   <si>
-    <t xml:space="preserve">Matheus Josué de Souza Matos; Geraldo Lúcio de Faria; Taíse Matte Manhabosco; Thiago Cazati; Fernado Gabriel; Eliane Ayres</t>
+    <t xml:space="preserve">Matheus Josué de Souza Matos; Geraldo Lúcio de Faria; Taíse Matte Manhabosco; Thiago Cazati; Eliane Ayres</t>
   </si>
   <si>
     <t xml:space="preserve">Relações entre processamento, estrutura, propriedades e desempenho de materiais. Estrutura atômica e ligações. Estruturas cristalinas e amorfas; defeitos pontuais, lineares, planares e interfaces. Difusão. Diagramas de fases e fundamentos de transformações. Introdução às propriedades mecânicas, térmicas, elétricas, magnéticas e ópticas. Visão comparativa de metais, cerâmicos, polímeros, compósitos e materiais funcionais. Seleção de materiais e relação com requisitos de engenharia, sustentabilidade e ciclo de vida. Estudos de caso integrando estrutura, processamento, propriedades e aplicação</t>
@@ -379,7 +379,7 @@
     <t xml:space="preserve">Metodologia da Pesquisa Científica</t>
   </si>
   <si>
-    <t xml:space="preserve">Versiane Albis Leão; Américo Tristão; Dalila Chaves Sicupira</t>
+    <t xml:space="preserve">Versiane Albis Leão; Américo Tristão Bernardes; Dalila Chaves Sicupira</t>
   </si>
   <si>
     <t xml:space="preserve">Natureza da pesquisa científica e tecnológica em Engenharia. Formulação de problema, hipótese, pergunta de pesquisa e objetivos. Estado da arte e revisão crítica da literatura; estratégias de busca, bases bibliográficas e rastreabilidade. Desenho metodológico, validação, reprodutibilidade, incerteza e gestão de dados. Integridade científica, autoria, plágio, conflitos de interesse, ética e uso responsável de ferramentas de inteligência artificial. Estrutura de projetos, dissertações, teses e artigos. Comunicação científica, revisão por pares, ciência aberta, dados FAIR e repositórios. Planejamento de pesquisa, cronograma, riscos e documentação</t>
@@ -406,9 +406,6 @@
     <t xml:space="preserve">Fundamentos em Inovação Tecnológica – Patentes</t>
   </si>
   <si>
-    <t xml:space="preserve">Patentes — Marcelo Gomes Speziali; gestão; tecnologias e mercado— Marcelo Gomes Speziali; Rodrigo Bianchi; Rita de Castro Engler</t>
-  </si>
-  <si>
     <t xml:space="preserve">Este curso apresenta um panorama atualizado do arcabouço legal que fundamenta o sistema de propriedade industrial, destacando a relevância das patentes no processo de decisão empresarial e acadêmico, bem como as formas de proteção de criações técnicas. Aborda a elaboração e tramitação de documentos de patente, desde a definição de critérios de patenteabilidade até a estrutura do relatório descritivo, além do uso de patentes como fonte de informação científica e tecnológica. O conteúdo foca especificamente as áreas das ciências duras e deeptechs, tratando de tipos de proteção intelectual, diferenças entre invenções e descobertas, estratégias de publicação versus proteção, custos e royalties de tecnologias, bem como processos de depósito nacional e internacional (PCT), ilustrados por estudos de caso. A disciplina aborda também questões relacionadas à gestão da inovação e sua relação com a propriedade intelectual</t>
   </si>
   <si>
@@ -421,6 +418,9 @@
     <t xml:space="preserve">Fundamentos em Inovação tecnológica - Gestão, Tecnologias e Mercado</t>
   </si>
   <si>
+    <t xml:space="preserve">Marcelo Gomes Speziali; Rodrigo Fernando Bianchi; Rita de Castro Engler</t>
+  </si>
+  <si>
     <t xml:space="preserve">A disciplina Fundamentos da Inovação Tecnológica: Gestão, Tecnologias e Estratégias de Mercado tem como objetivo capacitar estudantes de pós-graduação das áreas de ciências exatas, biológicas e engenharias a compreenderem os principais conceitos, modelos e ferramentas relacionados à inovação tecnológica, desde sua fundamentação teórica até sua aplicação prática no mercado. Serão abordados temas como ciência básica e pesquisa aplicada, modelos lineares e não lineares de inovação, escalas de maturidade (TRL e IRL), transferência de tecnologia, propriedade intelectual, estratégias de negócios (B2B, B2C, B2G), economia circular, inovação orientada à missão, além de políticas públicas e ecossistemas de inovação. A disciplina também promove o desenvolvimento de competências para atuar em ambientes interdisciplinares e inovadores, com ênfase na sustentabilidade, escalabilidade e impacto da ciência na sociedade</t>
   </si>
   <si>
@@ -466,7 +466,7 @@
     <t xml:space="preserve">Processamento, Manufatura e Engenharia de Superfícies</t>
   </si>
   <si>
-    <t xml:space="preserve">Geraldo Lúcio de Faria; Fernando Gabriel da Silva Araújo; Rodrigo Porcaro</t>
+    <t xml:space="preserve">Geraldo Lúcio de Faria; Fernando Gabriel da Silva Araújo; Rodrigo Rangel Porcaro</t>
   </si>
   <si>
     <t xml:space="preserve">Fundamentos comuns aos processos de transformação de materiais: termodinâmica, cinética, transporte de calor e massa e evolução microestrutural. Solidificação, conformação, sinterização, processamento de pós, rotas de processamento de polímeros e compósitos e processamento de materiais avançados. Relações processo–estrutura–propriedade. Seleção de rota, janelas de processamento, defeitos, eficiência energética, controle de processo e escalonamento. Integração entre processamento convencional, manufatura avançada e caracterização</t>
@@ -520,6 +520,9 @@
     <t xml:space="preserve">Engenharia de Superfícies e Revestimentos</t>
   </si>
   <si>
+    <t xml:space="preserve">Taíse Matte Manhabosco; Dalila Chaves Sicupira</t>
+  </si>
+  <si>
     <t xml:space="preserve">Superfície, interface e energia superficial. Relação entre estado superficial e mecanismos de degradação. Preparação e modificação de superfícies. Tratamentos termoquímicos, conversão química/eletroquímica, deposição física e química de vapor, aspersão térmica, eletrodeposição, sol-gel e técnicas a laser/plasma. Filmes finos e revestimentos funcionais. Adesão, tensões residuais e arquitetura de revestimentos. Caracterização química, estrutural, topográfica, mecânica e tribológica de superfícies. Seleção de processos para controle de corrosão, desgaste e funcionalização</t>
   </si>
   <si>
@@ -574,7 +577,7 @@
     <t xml:space="preserve">Tecnologia dos Materiais Poliméricos e Compósitos</t>
   </si>
   <si>
-    <t xml:space="preserve">Cláudio Gouvea dos Santos; Eliane Ayres</t>
+    <t xml:space="preserve">Claudio Gouvea dos Santos; Eliane Ayres</t>
   </si>
   <si>
     <t xml:space="preserve">Estrutura molecular, arquitetura macromolecular, massa molar e distribuição de massas molares. Morfologia, cristalinidade e transições térmicas. Relações entre estrutura, processamento, microestrutura e propriedades. Viscoelasticidade e reologia de polímeros. Processamento de termoplásticos, termofixos e elastômeros. Blendas, aditivos, modificação e degradação de polímeros. Fundamentos de materiais compósitos: matrizes, reforços, interfaces e transferência de tensão. Micromecânica, anisotropia, laminados e mecanismos de falha. Processamento de compósitos poliméricos e híbridos. Nanocompósitos, biopolímeros e compósitos de fontes renováveis. Reciclagem, sustentabilidade, economia circular e aplicações funcionais de materiais poliméricos e compósitos</t>
@@ -613,10 +616,6 @@
     <t xml:space="preserve">Lingotamento Contínuo De Aços</t>
   </si>
   <si>
-    <t xml:space="preserve">Johne Jesus Mol Peixoto .
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">Introdução e descrição do processo. Transferência de calor e solidificação no molde: Resfriamento no molde e resultados de sondagens; resfriamento secundário e terciário; modelo analítico e numérico; espessura mínima; influência de parâmetros operacionais sobre as trocas térmicas. Lubrificantes para lingotamento contínuo: funções e propriedades; especificação e consumo; influência sobre a operação. Características do ciclo de operação. Padrão de fluxo no molde e qualidade. Fenômenos de solidificação, tensões termomecânicas e formação de defeitos</t>
   </si>
   <si>
@@ -647,6 +646,9 @@
     <t xml:space="preserve">Comportamento Mecânico dos Materiais</t>
   </si>
   <si>
+    <t xml:space="preserve">Leonardo Barbosa Godefroid; Geraldo Lúcio de Faria</t>
+  </si>
+  <si>
     <t xml:space="preserve">Estados de tensão e deformação. Abordagem mecânica para elasticidade, viscoelasticidade e plasticidade. Discordâncias e micromecanismos de deformação plástica. Discordâncias e micromecanismos de endurecimento. Fratura: aspectos microestruturais e aplicação da Mecânica de Fratura. Fadiga. Fluência. Efeitos ambientais. Ensaios mecânicos</t>
   </si>
   <si>
@@ -671,6 +673,9 @@
     <t xml:space="preserve">Estrutura Eletrônica e Métodos Quânticos em Materiais</t>
   </si>
   <si>
+    <t xml:space="preserve">Matheus Josué de Souza Matos; Alan Barros de Oliveira; Américo Tristão Bernardes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fundamentos de DFT, condições periódicas/supercélulas aplicadas a primeiros princípios, defeitos e interfaces via cálculos ab initio, convergência e validação, estudos de caso em materiais funcionais</t>
   </si>
   <si>
@@ -683,6 +688,9 @@
     <t xml:space="preserve">Modelagem Atomística e Mesoscópica de Materiais</t>
   </si>
   <si>
+    <t xml:space="preserve">Matheus Josué de Souza Matos; Alan Barros de Oliveira</t>
+  </si>
+  <si>
     <t xml:space="preserve">Potenciais interatômicos, dinâmica molecular e Monte Carlo, métodos de mesoescala (phase-field) e conexão com contínuo/FEM, amostragem/convergência/quantificação de incerteza, fluxos reprodutíveis, HPC e integração com bases de dados/aprendizado de máquina, estudos de caso em metálicos, 2D e interfaces</t>
   </si>
   <si>
@@ -707,9 +715,6 @@
     <t xml:space="preserve">Inteligência Artificial e Ciência de Dados em Materiais</t>
   </si>
   <si>
-    <t xml:space="preserve">Matheus Josué de Souza Matos; Alan Barros de Oliveira; Américo Tristão Bernardes</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fundamentos de ciência de dados para materiais: aquisição, limpeza, normalização, curadoria e representação de dados. Descritores e engenharia de atributos. Aprendizado supervisionado e não supervisionado; regressão, classificação, redução de dimensionalidade e agrupamento. Validação cruzada, métricas, seleção de modelos, vieses, incerteza e interpretabilidade. Redes neurais e representações de grafos. Otimização bayesiana e active learning. Integração de literatura, bancos de dados experimentais e simulações. Materials informatics, descoberta inversa, modelos substitutos e desenho de experimentos. Reprodutibilidade, governança e limitações de IA generativa em pesquisa</t>
   </si>
   <si>
@@ -776,6 +781,9 @@
     <t xml:space="preserve">Mineração Urbana</t>
   </si>
   <si>
+    <t xml:space="preserve">Versiane Albis Leão; Paulo Santos Assis</t>
+  </si>
+  <si>
     <t xml:space="preserve">Definições. Geração, caracterização e classificação de resíduos e produtos em fim de vida. Economia circular e a gestão de REEE. Indicadores. Rotas de pré-tratamento, separação física, concentração e recuperação química/metalúrgica. Mineração urbana e metais críticos. Fluxogramas de processo. Reciclagem de baterias, resíduos industriais/minerais e eletroeletrônicos (REEE). Estudos de caso: Lâmpadas de LED, imãs permanentes, baterias LiB e placas de circuito impresso (PCI)</t>
   </si>
   <si>
@@ -837,10 +845,6 @@
   </si>
   <si>
     <t xml:space="preserve">Princípios e Aplicações da Espectroscopia de Absorção e Fotoluminescência em Materiais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vítreos e de Tecnologia dos Materiais Poliméricos; Compósitos serão compartilhadas com a Linha 1.1; estrutura; função e aplicação.
-</t>
   </si>
   <si>
     <t xml:space="preserve">Fundamentos da interação da radiação eletromagnética com a matéria e suas aplicações na caracterização de materiais. Espectroscopia de absorção UV-Vis: transições eletrônicas em moléculas e materiais, probabilidade de transição e regras de seleção, princípio de Franck–Condon, lei de Beer–Lambert e suas aplicações, dependência da absorbância com a concentração, absorbância verdadeira, efeitos do meio e deslocamentos solvatocrômicos, além de princípios de instrumentação e aquisição de espectros de absorção. Espectroscopia de fotoluminescência: fundamentos da fluorescência e da fosforescência, transições radiativas e não radiativas, deslocamento de Stokes, espectros de emissão, eficiência quântica de fluorescência, processos fotofísicos intra e intermoleculares, técnicas de fluorescência no estado estacionário e resolvida no tempo, tempos de vida do estado excitado, constantes de decaimento radiativo e não radiativo e métodos experimentais para sua determinação. Atividades práticas envolvendo aquisição, tratamento e interpretação de espectros de absorção e fotoluminescência aplicados à caracterização de materiais orgânicos, inorgânicos e híbridos</t>
@@ -2275,13 +2279,13 @@
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
       <c r="H7" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="J7" s="7" t="s">
         <v>127</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>128</v>
       </c>
       <c r="K7" s="6" t="s">
         <v>104</v>
@@ -2289,10 +2293,10 @@
     </row>
     <row r="8" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>129</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>130</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>30</v>
@@ -2306,7 +2310,7 @@
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="H8" s="7" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>131</v>
@@ -2567,12 +2571,14 @@
       <c r="G16" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="H16" s="7"/>
+      <c r="H16" s="7" t="s">
+        <v>164</v>
+      </c>
       <c r="I16" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>104</v>
@@ -2580,10 +2586,10 @@
     </row>
     <row r="17" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>30</v>
@@ -2602,10 +2608,10 @@
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K17" s="6" t="s">
         <v>104</v>
@@ -2613,10 +2619,10 @@
     </row>
     <row r="18" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>30</v>
@@ -2634,13 +2640,13 @@
         <v>145</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>104</v>
@@ -2648,10 +2654,10 @@
     </row>
     <row r="19" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C19" s="7" t="n">
         <v>45</v>
@@ -2669,13 +2675,13 @@
         <v>145</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K19" s="6" t="s">
         <v>104</v>
@@ -2683,10 +2689,10 @@
     </row>
     <row r="20" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C20" s="7" t="n">
         <v>30</v>
@@ -2704,13 +2710,13 @@
         <v>145</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>104</v>
@@ -2718,10 +2724,10 @@
     </row>
     <row r="21" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C21" s="7" t="n">
         <v>45</v>
@@ -2742,10 +2748,10 @@
         <v>72</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>104</v>
@@ -2753,10 +2759,10 @@
     </row>
     <row r="22" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>45</v>
@@ -2775,10 +2781,10 @@
       </c>
       <c r="H22" s="7"/>
       <c r="I22" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>104</v>
@@ -2786,10 +2792,10 @@
     </row>
     <row r="23" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C23" s="7" t="n">
         <v>45</v>
@@ -2807,7 +2813,7 @@
         <v>145</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>195</v>
+        <v>59</v>
       </c>
       <c r="I23" s="7" t="s">
         <v>196</v>
@@ -2876,12 +2882,14 @@
       <c r="G25" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="H25" s="7"/>
+      <c r="H25" s="7" t="s">
+        <v>206</v>
+      </c>
       <c r="I25" s="7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K25" s="6" t="s">
         <v>104</v>
@@ -2889,10 +2897,10 @@
     </row>
     <row r="26" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C26" s="7" t="n">
         <v>45</v>
@@ -2911,10 +2919,10 @@
       </c>
       <c r="H26" s="7"/>
       <c r="I26" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K26" s="6" t="s">
         <v>104</v>
@@ -2922,10 +2930,10 @@
     </row>
     <row r="27" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C27" s="7" t="n">
         <v>30</v>
@@ -2942,12 +2950,14 @@
       <c r="G27" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="H27" s="7"/>
+      <c r="H27" s="7" t="s">
+        <v>215</v>
+      </c>
       <c r="I27" s="7" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>104</v>
@@ -2955,10 +2965,10 @@
     </row>
     <row r="28" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C28" s="7" t="n">
         <v>30</v>
@@ -2975,12 +2985,14 @@
       <c r="G28" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="H28" s="7"/>
+      <c r="H28" s="7" t="s">
+        <v>220</v>
+      </c>
       <c r="I28" s="7" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>104</v>
@@ -2988,10 +3000,10 @@
     </row>
     <row r="29" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C29" s="7" t="n">
         <v>45</v>
@@ -3009,13 +3021,13 @@
         <v>201</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>104</v>
@@ -3023,10 +3035,10 @@
     </row>
     <row r="30" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C30" s="7" t="n">
         <v>45</v>
@@ -3044,13 +3056,13 @@
         <v>201</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>104</v>
@@ -3058,10 +3070,10 @@
     </row>
     <row r="31" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C31" s="7" t="n">
         <v>45</v>
@@ -3070,22 +3082,22 @@
         <v>3</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>104</v>
@@ -3093,10 +3105,10 @@
     </row>
     <row r="32" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C32" s="7" t="n">
         <v>45</v>
@@ -3105,22 +3117,22 @@
         <v>3</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>104</v>
@@ -3128,10 +3140,10 @@
     </row>
     <row r="33" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C33" s="7" t="n">
         <v>45</v>
@@ -3140,22 +3152,22 @@
         <v>3</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>104</v>
@@ -3163,10 +3175,10 @@
     </row>
     <row r="34" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C34" s="7" t="n">
         <v>30</v>
@@ -3175,20 +3187,22 @@
         <v>2</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="H34" s="7"/>
+        <v>235</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>251</v>
+      </c>
       <c r="I34" s="7" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>104</v>
@@ -3196,10 +3210,10 @@
     </row>
     <row r="35" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C35" s="7" t="n">
         <v>45</v>
@@ -3208,22 +3222,22 @@
         <v>3</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>104</v>
@@ -3231,10 +3245,10 @@
     </row>
     <row r="36" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C36" s="7" t="n">
         <v>30</v>
@@ -3243,22 +3257,22 @@
         <v>2</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>104</v>
@@ -3266,10 +3280,10 @@
     </row>
     <row r="37" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C37" s="7" t="n">
         <v>30</v>
@@ -3278,22 +3292,22 @@
         <v>2</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>104</v>
@@ -3301,10 +3315,10 @@
     </row>
     <row r="38" customFormat="false" ht="169.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C38" s="7" t="n">
         <v>30</v>
@@ -3313,22 +3327,22 @@
         <v>2</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>270</v>
+        <v>82</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>104</v>
@@ -3336,10 +3350,10 @@
     </row>
     <row r="39" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C39" s="7" t="n">
         <v>45</v>
@@ -3348,22 +3362,22 @@
         <v>3</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>104</v>
@@ -3371,10 +3385,10 @@
     </row>
     <row r="40" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C40" s="7" t="n">
         <v>30</v>
@@ -3383,22 +3397,22 @@
         <v>2</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>104</v>
